--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486341_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486341_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. CAMACHO DE SÁ</t>
+          <t>A. COMENDADOR FEMENIAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8022</v>
+        <v>5.4234</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8546</v>
+        <v>3.0044</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9476</v>
+        <v>2.419</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3285</v>
+        <v>2.5067</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.7091</v>
+        <v>1.0126</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0376</v>
+        <v>1.4941</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3542</v>
+        <v>2.7969</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.1918</v>
+        <v>1.4964</v>
       </c>
       <c r="L2" t="n">
-        <v>2.546</v>
+        <v>1.3005</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0257</v>
+        <v>-0.2902</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5173</v>
+        <v>-0.4838</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4916</v>
+        <v>0.1936</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.5225</v>
       </c>
       <c r="R2" t="n">
-        <v>2.6101</v>
+        <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3875</v>
+        <v>-0.2133</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8723</v>
+        <v>-0.5299</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5153</v>
+        <v>0.3166</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9986</v>
+        <v>2.2599</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1507</v>
+        <v>2.2599</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. COMENDADOR FEMENIAS</t>
+          <t>N. CAMACHO DE SÁ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1245</v>
+        <v>4.9835</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6439</v>
+        <v>2.0975</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4806</v>
+        <v>2.886</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5067</v>
+        <v>1.3285</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0126</v>
+        <v>-1.7091</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4941</v>
+        <v>3.0376</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7969</v>
+        <v>1.3542</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4964</v>
+        <v>-1.1918</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3005</v>
+        <v>2.546</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2902</v>
+        <v>-0.0257</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4838</v>
+        <v>-0.5173</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1936</v>
+        <v>0.4916</v>
       </c>
       <c r="P3" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.5225</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3926</v>
+        <v>2.6101</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5122</v>
+        <v>1.5688</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8904</v>
+        <v>1.1152</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3783</v>
+        <v>0.4536</v>
       </c>
       <c r="V3" t="n">
-        <v>2.2599</v>
+        <v>0.9986</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2599</v>
+        <v>1.1507</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.152</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5653</v>
+        <v>1.1752</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.8728</v>
+        <v>-3.1395</v>
       </c>
       <c r="F4" t="n">
-        <v>4.4381</v>
+        <v>4.3148</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4655</v>
@@ -766,13 +766,13 @@
         <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7264</v>
+        <v>1.3363</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9782</v>
+        <v>0.7114</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7482</v>
+        <v>0.6249</v>
       </c>
       <c r="V4" t="n">
         <v>0.7395</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0697</v>
+        <v>0.8958</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0024</v>
+        <v>0.4699</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0673</v>
+        <v>0.4259</v>
       </c>
       <c r="G5" t="n">
         <v>-3.0616</v>
@@ -844,13 +844,13 @@
         <v>3.0451</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1831</v>
+        <v>0.7823</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1767</v>
+        <v>0.6489</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3598</v>
+        <v>0.1334</v>
       </c>
       <c r="V5" t="n">
         <v>0.5649999999999999</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5206</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5037</v>
+        <v>-0.8137</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0169</v>
+        <v>0.168</v>
       </c>
       <c r="G6" t="n">
         <v>-1.9375</v>
@@ -922,13 +922,13 @@
         <v>2.8276</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4814</v>
+        <v>0.3563</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.5312</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3598</v>
+        <v>-0.1749</v>
       </c>
       <c r="V6" t="n">
         <v>-0.152</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0822</v>
+        <v>-1.3055</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.148</v>
+        <v>-4.3405</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0658</v>
+        <v>3.035</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6121</v>
@@ -1000,13 +1000,13 @@
         <v>3.4801</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6405999999999999</v>
+        <v>0.1361</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0719</v>
+        <v>-0.2644</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4313</v>
+        <v>0.4004</v>
       </c>
       <c r="V7" t="n">
         <v>2.8681</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8185</v>
+        <v>-3.1662</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0318</v>
+        <v>-2.4104</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7867</v>
+        <v>-0.7558</v>
       </c>
       <c r="G8" t="n">
         <v>-2.5278</v>
@@ -1078,13 +1078,13 @@
         <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4916</v>
+        <v>0.1439</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4711</v>
+        <v>0.0925</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3473</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6415</v>
+        <v>-3.3918</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9158</v>
+        <v>-2.5121</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7256</v>
+        <v>-0.8797</v>
       </c>
       <c r="G9" t="n">
         <v>-1.2257</v>
@@ -1156,13 +1156,13 @@
         <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3887</v>
+        <v>0.6384</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1815</v>
+        <v>0.2223</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5702</v>
+        <v>0.4161</v>
       </c>
       <c r="V9" t="n">
         <v>-1.282</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.842</v>
+        <v>-4.4237</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.4073</v>
+        <v>-4.7115</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5653</v>
+        <v>0.2879</v>
       </c>
       <c r="G10" t="n">
         <v>-4.1175</v>
@@ -1234,13 +1234,13 @@
         <v>1.9576</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.07199999999999999</v>
+        <v>0.3464</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7294</v>
+        <v>-0.0336</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6574</v>
+        <v>0.38</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.482499999999999</v>
+        <v>-0.4550000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-13.3833</v>
+        <v>-12.3559</v>
       </c>
       <c r="F11" t="n">
-        <v>11.9009</v>
+        <v>11.9011</v>
       </c>
       <c r="G11" t="n">
         <v>-10.1125</v>
@@ -1312,13 +1312,13 @@
         <v>19.5757</v>
       </c>
       <c r="S11" t="n">
-        <v>4.0677</v>
+        <v>5.0952</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4663</v>
+        <v>2.4936</v>
       </c>
       <c r="U11" t="n">
-        <v>2.6016</v>
+        <v>2.6015</v>
       </c>
       <c r="V11" t="n">
         <v>5.649800000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.1835</v>
+        <v>5.5945</v>
       </c>
       <c r="E12" t="n">
-        <v>4.5024</v>
+        <v>2.8261</v>
       </c>
       <c r="F12" t="n">
-        <v>2.681</v>
+        <v>2.7684</v>
       </c>
       <c r="G12" t="n">
         <v>2.6653</v>
@@ -1390,13 +1390,13 @@
         <v>1.9576</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5606</v>
+        <v>0.9716</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3638</v>
+        <v>0.6874</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1968</v>
+        <v>0.2842</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.0417</v>
+        <v>3.9851</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2555</v>
+        <v>1.8085</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7861</v>
+        <v>2.1766</v>
       </c>
       <c r="G13" t="n">
         <v>4.2851</v>
@@ -1468,13 +1468,13 @@
         <v>2.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8084</v>
+        <v>-0.8649</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0769</v>
+        <v>-0.5239</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7315</v>
+        <v>-0.341</v>
       </c>
       <c r="V13" t="n">
         <v>0.5649999999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. GIOVANNETTI</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0873</v>
+        <v>3.0299</v>
       </c>
       <c r="E14" t="n">
-        <v>1.299</v>
+        <v>-0.8006</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7883</v>
+        <v>3.8305</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7841</v>
+        <v>2.7087</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8765</v>
+        <v>1.1405</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0924</v>
+        <v>1.5682</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5729</v>
+        <v>2.0738</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4964</v>
+        <v>1.2108</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0765</v>
+        <v>0.863</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2111</v>
+        <v>0.6349</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3801</v>
+        <v>-0.0703</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1689</v>
+        <v>0.7052</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q14" t="n">
+        <v>-2.1751</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3.0451</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.5489000000000001</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.6994</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.1505</v>
+      </c>
+      <c r="V14" t="n">
         <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.0875</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-0.2193</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-0.274</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.0547</v>
-      </c>
-      <c r="V14" t="n">
-        <v>-0.5649999999999999</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>L. GIOVANNETTI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5732</v>
+        <v>2.194</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.4712</v>
+        <v>1.4107</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0444</v>
+        <v>0.7832</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7087</v>
+        <v>1.7841</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1405</v>
+        <v>1.8765</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5682</v>
+        <v>-0.0924</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0738</v>
+        <v>1.5729</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2108</v>
+        <v>1.4964</v>
       </c>
       <c r="L15" t="n">
-        <v>0.863</v>
+        <v>0.0765</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6349</v>
+        <v>0.2111</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0703</v>
+        <v>0.3801</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7052</v>
+        <v>-0.1689</v>
       </c>
       <c r="P15" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.0451</v>
+        <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.0055</v>
+        <v>-0.1127</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3699</v>
+        <v>-0.1622</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6356000000000001</v>
+        <v>0.0496</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5026</v>
+        <v>1.2232</v>
       </c>
       <c r="E16" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.4257</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4121</v>
+        <v>0.7975</v>
       </c>
       <c r="G16" t="n">
         <v>1.4035</v>
@@ -1702,13 +1702,13 @@
         <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6612</v>
+        <v>0.0595</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.822</v>
+        <v>-0.4867</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1608</v>
+        <v>0.5462</v>
       </c>
       <c r="V16" t="n">
         <v>0.1952</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7331</v>
+        <v>0.5938</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0531</v>
+        <v>-0.2708</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3199</v>
+        <v>0.8645</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4283</v>
@@ -1780,13 +1780,13 @@
         <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9796</v>
+        <v>0.3473</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8904</v>
+        <v>-0.1081</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0892</v>
+        <v>0.4554</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1952</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0975</v>
+        <v>-1.109</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9943</v>
+        <v>-1.8825</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8968</v>
+        <v>0.7735</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0462</v>
@@ -1858,13 +1858,13 @@
         <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1233</v>
+        <v>0.1118</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2055</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3288</v>
+        <v>0.2055</v>
       </c>
       <c r="V18" t="n">
         <v>-0.7395</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.381</v>
+        <v>-1.7799</v>
       </c>
       <c r="E19" t="n">
         <v>-3.1255</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7445000000000001</v>
+        <v>1.3456</v>
       </c>
       <c r="G19" t="n">
         <v>1.4228</v>
@@ -1936,13 +1936,13 @@
         <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4559</v>
+        <v>-0.8547</v>
       </c>
       <c r="T19" t="n">
         <v>-0.548</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9079</v>
+        <v>-0.3067</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3904</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1405</v>
+        <v>-2.7745</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7913</v>
+        <v>-2.9031</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3492</v>
+        <v>0.1287</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1491</v>
@@ -2014,13 +2014,13 @@
         <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4265</v>
+        <v>-0.0604</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.1202</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4181</v>
+        <v>0.0598</v>
       </c>
       <c r="V20" t="n">
         <v>-1.13</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. GRANGER</t>
+          <t>J. VAULET</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2656</v>
+        <v>-3.0696</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.0183</v>
+        <v>-4.3711</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7528</v>
+        <v>1.3014</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2367</v>
+        <v>-0.2968</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0487</v>
+        <v>1.0037</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2854</v>
+        <v>-1.3005</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.5609</v>
+        <v>-0.1046</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2309</v>
+        <v>1.156</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.33</v>
+        <v>-1.2606</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3242</v>
+        <v>-0.1922</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2796</v>
+        <v>-0.1523</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0446</v>
+        <v>-0.0399</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2175</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3926</v>
+        <v>2.6101</v>
       </c>
       <c r="S21" t="n">
-        <v>0.274</v>
+        <v>-0.2509</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2824</v>
+        <v>-0.2644</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5564</v>
+        <v>0.0135</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5204</v>
+        <v>-1.8695</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.5204</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. VAULET</t>
+          <t>J. GRANGER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.288</v>
+        <v>-3.4248</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.5946</v>
+        <v>-5.0183</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3065</v>
+        <v>1.5935</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2968</v>
+        <v>-2.2367</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0037</v>
+        <v>0.0487</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3005</v>
+        <v>-2.2854</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1046</v>
+        <v>-2.5609</v>
       </c>
       <c r="K22" t="n">
-        <v>1.156</v>
+        <v>-0.2309</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2606</v>
+        <v>-2.33</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1922</v>
+        <v>0.3242</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1523</v>
+        <v>0.2796</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0399</v>
+        <v>0.0446</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>2.6101</v>
+        <v>2.3926</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4693</v>
+        <v>0.1148</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4879</v>
+        <v>-0.2824</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0186</v>
+        <v>0.3972</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8695</v>
+        <v>-1.5204</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.13</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.482600000000001</v>
+        <v>4.462700000000002</v>
       </c>
       <c r="E23" t="n">
-        <v>-11.901</v>
+        <v>-11.9009</v>
       </c>
       <c r="F23" t="n">
-        <v>13.3832</v>
+        <v>16.3634</v>
       </c>
       <c r="G23" t="n">
         <v>10.1124</v>
@@ -2227,7 +2227,7 @@
         <v>8.563699999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.02369999999999961</v>
+        <v>-0.02369999999999983</v>
       </c>
       <c r="M23" t="n">
         <v>1.5726</v>
@@ -2248,22 +2248,22 @@
         <v>20.6633</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.067799999999999</v>
+        <v>-1.0875</v>
       </c>
       <c r="T23" t="n">
         <v>-2.6016</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.4662</v>
+        <v>1.5142</v>
       </c>
       <c r="V23" t="n">
-        <v>-5.6498</v>
+        <v>-5.649800000000001</v>
       </c>
       <c r="W23" t="n">
         <v>1.736399999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-7.3862</v>
+        <v>-7.386199999999999</v>
       </c>
     </row>
   </sheetData>
